--- a/labs/lab4-porter/ЛР4_Портер_SimilarWeb_DiagramCode.xlsx
+++ b/labs/lab4-porter/ЛР4_Портер_SimilarWeb_DiagramCode.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>Сила</t>
   </si>
@@ -123,10 +123,10 @@
     <t>5 игроков идентифицированы в ЛР5</t>
   </si>
   <si>
-    <t>Концентрация трафика (CR3/CR5)</t>
-  </si>
-  <si>
-    <t>НЕ РАССЧИТАНО — полные данные SimilarWeb только по 2 из 5 доменов (лимит бесплатного тарифа)</t>
+    <t>Концентрация трафика (CR-4 по измеренным доменам)</t>
+  </si>
+  <si>
+    <t>CR-4=99,99% по 4 доменам с данными SimilarWeb (app.diagrams.net 86,6%+eraser.io 7,5%+plantuml.com 5,6%+mermaidchart.com 0,2%, снято 2026-09-23) — не эквивалент полного CR3/CR5 по всей категории (D2/Lucidchart/Visio не входят)</t>
   </si>
   <si>
     <t>Стоимость входа в каналы</t>
@@ -808,8 +808,8 @@
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
+      <c r="B3" s="1">
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>37</v>
